--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="493">
   <si>
     <t>Filename</t>
   </si>
@@ -811,691 +811,688 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9696,0.0033,0.0077,0.0019</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9712,0.0001,0.0001,0.0329</t>
-  </si>
-  <si>
-    <t>0.0036,0.0000,0.0001,0.9987</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
+    <t>0.9649,0.0083,0.0073,0.0011</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9435,0.0002,0.0001,0.0631</t>
+  </si>
+  <si>
+    <t>0.3465,0.0001,0.0002,0.8495</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0009,0.0002,0.0001</t>
+    <t>0.9973,0.0022,0.0001,0.0000</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.8623,0.0149,0.0601,0.0012</t>
-  </si>
-  <si>
-    <t>0.0204,0.0057,0.9596,0.0008</t>
-  </si>
-  <si>
-    <t>0.0787,0.0002,0.9648,0.0000</t>
-  </si>
-  <si>
-    <t>0.6635,0.0001,0.4490,0.0001</t>
-  </si>
-  <si>
-    <t>0.8722,0.0004,0.1164,0.0007</t>
+    <t>0.9970,0.0002,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0040,0.0006,0.9921,0.0009</t>
+  </si>
+  <si>
+    <t>0.0936,0.0005,0.9610,0.0000</t>
+  </si>
+  <si>
+    <t>0.0356,0.0003,0.9798,0.0001</t>
+  </si>
+  <si>
+    <t>0.9667,0.0009,0.0245,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.9967,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0909,0.0013,0.8837,0.0028</t>
+  </si>
+  <si>
+    <t>0.1436,0.0002,0.8658,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0003,0.9981,0.0004</t>
+  </si>
+  <si>
+    <t>0.0092,0.0001,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0001,0.9955,0.0004</t>
+  </si>
+  <si>
+    <t>0.0378,0.0001,0.9783,0.0002</t>
+  </si>
+  <si>
+    <t>0.2639,0.7881,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.7832,0.0125,0.1457,0.0013</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.9991,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0003,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0979,0.9233,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9954,0.5845,0.0000</t>
+  </si>
+  <si>
+    <t>0.0046,0.9878,0.0040,0.0004</t>
+  </si>
+  <si>
+    <t>0.0038,0.0000,0.9940,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.0077,0.9951,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0009,0.9951,0.0015</t>
+  </si>
+  <si>
+    <t>0.0013,0.0454,0.9960,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9987,0.0013</t>
+  </si>
+  <si>
+    <t>0.0011,0.8686,0.0005,0.9602</t>
+  </si>
+  <si>
+    <t>0.0021,0.9963,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.9962,0.0027,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9996,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0008,0.9965,0.0008</t>
+  </si>
+  <si>
+    <t>0.0251,0.0001,0.9888,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0006,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9836,0.0192,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9972,0.9847,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0040,0.9980,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9939,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.7048,0.0002,0.4333,0.0001</t>
+  </si>
+  <si>
+    <t>0.7967,0.0026,0.1480,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.0012,0.9992,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.5235,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.8571,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9905,0.9828,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0016,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0011,0.9998</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9951,0.9792,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.9936,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9741,0.9145,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9900,0.9793,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9947,0.9934,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9915,0.3464,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0012,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9936,0.0036,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9953,0.0032,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0002,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0153,0.0028,0.9782,0.0003</t>
+  </si>
+  <si>
+    <t>0.9832,0.0004,0.0064,0.0004</t>
+  </si>
+  <si>
+    <t>0.0098,0.0002,0.9905,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9996,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0236,0.9784,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9983,0.0002,0.0023</t>
-  </si>
-  <si>
-    <t>0.7203,0.0001,0.2001,0.0026</t>
-  </si>
-  <si>
-    <t>0.8502,0.0011,0.1409,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0114,0.0004,0.9841,0.0006</t>
-  </si>
-  <si>
-    <t>0.8772,0.0001,0.1881,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0003,0.9972,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9991,0.0004</t>
-  </si>
-  <si>
-    <t>0.2665,0.7331,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.9943,0.0030,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0009,0.9993,0.0006</t>
-  </si>
-  <si>
-    <t>0.0013,0.9964,0.0027,0.0000</t>
-  </si>
-  <si>
-    <t>0.9931,0.0038,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.6922,0.0018,0.2979,0.0010</t>
-  </si>
-  <si>
-    <t>0.2409,0.8206,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.6460,0.0000</t>
-  </si>
-  <si>
-    <t>0.0143,0.9608,0.0074,0.0006</t>
-  </si>
-  <si>
-    <t>0.0018,0.0004,0.9949,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0012,0.9975,0.0001</t>
-  </si>
-  <si>
-    <t>0.0411,0.0002,0.9603,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0027,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9994,0.0023</t>
-  </si>
-  <si>
-    <t>0.0008,0.9224,0.0010,0.9457</t>
-  </si>
-  <si>
-    <t>0.0008,0.9976,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.0005,0.9982,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
+    <t>0.0039,0.9937,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9977,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.4063,0.6729,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.8249,0.0138,0.0721,0.0018</t>
+  </si>
+  <si>
+    <t>0.9748,0.0001,0.0243,0.0002</t>
+  </si>
+  <si>
+    <t>0.9441,0.0044,0.0093,0.0021</t>
+  </si>
+  <si>
+    <t>0.3736,0.0124,0.4935,0.0033</t>
+  </si>
+  <si>
+    <t>0.0045,0.7557,0.0067,0.8455</t>
+  </si>
+  <si>
+    <t>0.0006,0.9988,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9953,0.9755,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.2447,0.8057,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9101,0.1047,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0006,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9316,0.9959,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8777,0.9951,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0038,0.9962,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9314,0.0064,0.0073,0.0038</t>
+  </si>
+  <si>
+    <t>0.1082,0.0001,0.9332,0.0001</t>
+  </si>
+  <si>
+    <t>0.8041,0.0005,0.1817,0.0016</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9934,0.4918,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0136,0.9838,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.0166,0.9858,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9276,0.0000,0.0022,0.0441</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0015,0.9979,0.0014</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9941,0.0000,0.0025,0.0005</t>
+  </si>
+  <si>
+    <t>0.4786,0.2332,0.0562,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9703,0.0050,0.0080,0.0013</t>
+  </si>
+  <si>
+    <t>0.2020,0.0635,0.2994,0.0014</t>
+  </si>
+  <si>
+    <t>0.7441,0.0042,0.1642,0.0005</t>
+  </si>
+  <si>
+    <t>0.9938,0.0010,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0008,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9508,0.0328,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9484,0.0651,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.7876,0.2463,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.3012,0.0002,0.7378,0.0006</t>
+  </si>
+  <si>
+    <t>0.9870,0.0149,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9980,0.0011,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9823,0.0026,0.0075,0.0011</t>
+  </si>
+  <si>
+    <t>0.0017,0.0003,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0007,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.0154,0.9947,0.0021</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.2696,0.9883,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.1490,0.0015,0.8840,0.0004</t>
+  </si>
+  <si>
+    <t>0.0088,0.0007,0.9901,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.0036,0.9946,0.0001</t>
+  </si>
+  <si>
+    <t>0.5936,0.0081,0.3978,0.0003</t>
+  </si>
+  <si>
+    <t>0.2687,0.0533,0.3955,0.0008</t>
+  </si>
+  <si>
+    <t>0.9754,0.0006,0.0244,0.0001</t>
+  </si>
+  <si>
+    <t>0.9544,0.0014,0.0197,0.0016</t>
+  </si>
+  <si>
+    <t>0.0992,0.0225,0.8464,0.0009</t>
+  </si>
+  <si>
+    <t>0.0019,0.9970,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9985,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5818,0.4509,0.0040,0.0001</t>
+  </si>
+  <si>
+    <t>0.1688,0.8749,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0124,0.9871,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9942,0.0009,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9842,0.0001,0.0191,0.0001</t>
+  </si>
+  <si>
+    <t>0.9648,0.0014,0.0015,0.0054</t>
+  </si>
+  <si>
+    <t>0.9094,0.0132,0.0312,0.0024</t>
+  </si>
+  <si>
+    <t>0.8153,0.0005,0.1737,0.0009</t>
+  </si>
+  <si>
+    <t>0.0020,0.0006,0.9976,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9980,0.0004</t>
+  </si>
+  <si>
+    <t>0.0159,0.0009,0.9763,0.0010</t>
+  </si>
+  <si>
+    <t>0.0062,0.0041,0.9871,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.0720,0.9232,0.0006</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9940,0.0031,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0014,0.9994,0.0005</t>
+  </si>
+  <si>
+    <t>0.0081,0.0144,0.9770,0.0008</t>
+  </si>
+  <si>
+    <t>0.9701,0.0002,0.0151,0.0014</t>
+  </si>
+  <si>
+    <t>0.0065,0.0003,0.9974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.6002,0.9917,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0662,0.0004,0.9593,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.0495,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9990,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.0000,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0008,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9999,0.0004</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9193,0.1280,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9972,0.5467,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0007,0.9984,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9986,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9984,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9945,0.0002,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.1999,0.0001,0.8973,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9997,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9952,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.8095,0.9653,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.9832,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.9917,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0005,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0044,0.9992</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0016,0.9998</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9910,0.9751,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9961,0.9952,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9934,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9981,0.9887,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9132,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9960,0.6627,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0021,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9933,0.0057,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9962,0.0017,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9988,0.0016,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0028,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.9989,0.0004</t>
-  </si>
-  <si>
-    <t>0.0045,0.0007,0.9947,0.0001</t>
-  </si>
-  <si>
-    <t>0.8912,0.0005,0.0689,0.0042</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9986,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9973,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9985,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0781,0.9442,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.5863,0.0028,0.4052,0.0012</t>
-  </si>
-  <si>
-    <t>0.9884,0.0001,0.0072,0.0001</t>
-  </si>
-  <si>
-    <t>0.9577,0.0016,0.0173,0.0017</t>
-  </si>
-  <si>
-    <t>0.9909,0.0008,0.0010,0.0009</t>
-  </si>
-  <si>
-    <t>0.0044,0.3873,0.0008,0.9151</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9951,0.9047,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.3457,0.7140,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9688,0.0291,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0002,0.0007</t>
+    <t>0.0015,0.0002,0.9970,0.0011</t>
+  </si>
+  <si>
+    <t>0.0004,0.0047,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.3839,0.0023,0.6185,0.0009</t>
+  </si>
+  <si>
+    <t>0.9910,0.0002,0.0027,0.0002</t>
+  </si>
+  <si>
+    <t>0.9921,0.0002,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0019,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.9994,0.0001,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0005,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9961,0.0011,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.4557,0.9947,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9945,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0134,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0041,0.0015,0.9911,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.2111,0.0010,0.7427,0.0022</t>
-  </si>
-  <si>
-    <t>0.5229,0.0000,0.6045,0.0001</t>
-  </si>
-  <si>
-    <t>0.9857,0.0002,0.0035,0.0008</t>
-  </si>
-  <si>
-    <t>0.0084,0.0002,0.0000,0.9977</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0002,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.9834,0.8435,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0052,0.9923,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.6832,0.4677,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.1639,0.0001,0.0004,0.9230</t>
-  </si>
-  <si>
-    <t>0.0010,0.0009,0.9977,0.0034</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9912,0.0001,0.0062,0.0003</t>
-  </si>
-  <si>
-    <t>0.2447,0.7689,0.0047,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0002,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9895,0.0021,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.9141,0.0384,0.0053,0.0009</t>
-  </si>
-  <si>
-    <t>0.2695,0.0190,0.6951,0.0002</t>
-  </si>
-  <si>
-    <t>0.9919,0.0014,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9944,0.0013,0.0010,0.0017</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9702,0.0173,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9687,0.0426,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9745,0.0305,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0322,0.0014,0.9606,0.0026</t>
-  </si>
-  <si>
-    <t>0.9889,0.0102,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0009,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9818,0.0107,0.0046,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.9927,0.0018,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0062,0.9921,0.0048</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.0579,0.9832,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0157,0.0060,0.9699,0.0006</t>
-  </si>
-  <si>
-    <t>0.0093,0.0014,0.9892,0.0002</t>
-  </si>
-  <si>
-    <t>0.0533,0.0068,0.9426,0.0005</t>
-  </si>
-  <si>
-    <t>0.0269,0.0101,0.9365,0.0004</t>
-  </si>
-  <si>
-    <t>0.0377,0.0749,0.7702,0.0003</t>
-  </si>
-  <si>
-    <t>0.8728,0.0128,0.0907,0.0003</t>
-  </si>
-  <si>
-    <t>0.8955,0.0040,0.0289,0.0057</t>
-  </si>
-  <si>
-    <t>0.1114,0.0017,0.8959,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.9990,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.9972,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6211,0.4949,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.4183,0.7203,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0059,0.9921,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9314,0.0166,0.0108,0.0003</t>
-  </si>
-  <si>
-    <t>0.9764,0.0004,0.0104,0.0010</t>
-  </si>
-  <si>
-    <t>0.9507,0.0011,0.0134,0.0043</t>
-  </si>
-  <si>
-    <t>0.7124,0.0146,0.1818,0.0053</t>
-  </si>
-  <si>
-    <t>0.9677,0.0003,0.0285,0.0004</t>
-  </si>
-  <si>
-    <t>0.0066,0.0006,0.9937,0.0004</t>
-  </si>
-  <si>
-    <t>0.0011,0.0006,0.9967,0.0004</t>
-  </si>
-  <si>
-    <t>0.0183,0.0023,0.9659,0.0016</t>
-  </si>
-  <si>
-    <t>0.0139,0.0026,0.9784,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0031,0.9911,0.0009</t>
-  </si>
-  <si>
-    <t>0.9939,0.0039,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9953,0.0021,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9921,0.0098,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0023,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0011,0.9993,0.0005</t>
-  </si>
-  <si>
-    <t>0.0142,0.0199,0.9467,0.0015</t>
-  </si>
-  <si>
-    <t>0.8376,0.0003,0.0906,0.0040</t>
-  </si>
-  <si>
-    <t>0.0016,0.0002,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.1741,0.9846,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0045,0.0003,0.9940,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0011,0.9945,0.0003</t>
-  </si>
-  <si>
-    <t>0.0083,0.0174,0.9703,0.0015</t>
-  </si>
-  <si>
-    <t>0.9736,0.0007,0.0167,0.0003</t>
-  </si>
-  <si>
-    <t>0.9398,0.0002,0.0569,0.0005</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0016,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0062,0.0088,0.9822,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.0008,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.7708,0.9959,0.0001</t>
-  </si>
-  <si>
-    <t>0.0108,0.0071,0.9690,0.0016</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9922,0.0054</t>
-  </si>
-  <si>
-    <t>0.0104,0.0016,0.9857,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9974,0.0015</t>
-  </si>
-  <si>
-    <t>0.9904,0.0000,0.0015,0.0031</t>
-  </si>
-  <si>
-    <t>0.0009,0.0027,0.0000,0.9993</t>
-  </si>
-  <si>
-    <t>0.0318,0.0000,0.0000,0.9943</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0001,0.0000</t>
+    <t>0.9992,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0064,0.0135,0.9746,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.1417,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.0004,0.9948,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0171,0.0003,0.3839,0.2103</t>
+  </si>
+  <si>
+    <t>0.0495,0.0004,0.9518,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9978,0.0011</t>
+  </si>
+  <si>
+    <t>0.7859,0.0000,0.0006,0.3053</t>
+  </si>
+  <si>
+    <t>0.0024,0.0002,0.0000,0.9994</t>
+  </si>
+  <si>
+    <t>0.0544,0.0000,0.0000,0.9960</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0000,0.0001</t>
   </si>
 </sst>
 </file>
@@ -1951,7 +1948,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1965,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1979,7 +1976,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1993,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2007,7 +2004,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2021,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2035,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2049,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2063,7 +2060,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2077,7 +2074,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2088,10 +2085,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2105,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2119,7 +2116,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2133,7 +2130,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2147,7 +2144,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2161,7 +2158,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2175,7 +2172,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2186,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
         <v>284</v>
@@ -2200,7 +2197,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>285</v>
@@ -2242,7 +2239,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>288</v>
@@ -2637,7 +2634,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>272</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2651,7 +2648,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2665,7 +2662,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2679,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2693,7 +2690,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2707,7 +2704,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2721,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2844,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
         <v>330</v>
@@ -2973,7 +2970,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2987,7 +2984,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3001,7 +2998,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3015,7 +3012,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3029,7 +3026,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3043,7 +3040,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3057,7 +3054,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3071,7 +3068,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3082,10 +3079,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3099,7 +3096,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3113,7 +3110,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3127,7 +3124,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3141,7 +3138,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3155,7 +3152,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3169,7 +3166,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3183,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3197,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3211,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3225,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3239,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3253,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3267,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>354</v>
+        <v>316</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3281,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3295,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3309,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3323,7 +3320,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3337,7 +3334,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3351,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3365,7 +3362,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3379,7 +3376,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3393,7 +3390,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>280</v>
+        <v>359</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3407,7 +3404,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3421,7 +3418,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3435,7 +3432,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>364</v>
+        <v>279</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3449,7 +3446,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3463,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3477,7 +3474,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3491,7 +3488,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3505,7 +3502,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3519,7 +3516,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3530,10 +3527,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3547,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3561,7 +3558,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>309</v>
+        <v>370</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3575,7 +3572,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3589,7 +3586,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3603,7 +3600,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3617,7 +3614,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3631,7 +3628,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3645,7 +3642,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3659,7 +3656,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3673,7 +3670,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3687,7 +3684,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3701,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3715,7 +3712,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3729,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3743,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>270</v>
+        <v>383</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3754,10 +3751,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3771,7 +3768,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3785,7 +3782,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3799,7 +3796,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3813,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3824,10 +3821,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3841,7 +3838,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3855,7 +3852,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3869,7 +3866,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3883,7 +3880,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3897,7 +3894,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>395</v>
+        <v>337</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3911,7 +3908,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>338</v>
+        <v>393</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3922,10 +3919,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3939,7 +3936,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3953,7 +3950,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3967,7 +3964,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3978,10 +3975,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3995,7 +3992,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4006,10 +4003,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4023,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>270</v>
+        <v>400</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4037,7 +4034,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4051,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4065,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4076,10 +4073,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4093,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4107,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4121,7 +4118,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4132,10 +4129,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4149,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4163,7 +4160,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4177,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>412</v>
+        <v>380</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4191,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4205,7 +4202,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4219,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4233,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4247,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4261,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>270</v>
+        <v>413</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4275,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4289,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4303,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4317,7 +4314,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4331,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4345,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4359,7 +4356,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4373,7 +4370,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4387,7 +4384,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4401,7 +4398,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4415,7 +4412,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>427</v>
+        <v>326</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4429,7 +4426,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4443,7 +4440,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4457,7 +4454,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4471,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4485,7 +4482,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>432</v>
+        <v>326</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4499,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4513,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4527,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4541,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4552,10 +4549,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4566,10 +4563,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4583,7 +4580,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4597,7 +4594,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4611,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4625,7 +4622,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4639,7 +4636,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4653,7 +4650,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4667,7 +4664,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4681,7 +4678,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4695,7 +4692,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4709,7 +4706,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4723,7 +4720,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4737,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4751,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4765,7 +4762,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4779,7 +4776,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4793,7 +4790,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4807,7 +4804,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4821,7 +4818,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4835,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4849,7 +4846,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4863,7 +4860,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4877,7 +4874,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4891,7 +4888,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>411</v>
+        <v>457</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4905,7 +4902,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4919,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4933,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>462</v>
+        <v>380</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4947,7 +4944,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4961,7 +4958,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4975,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4989,7 +4986,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5003,7 +5000,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5014,10 +5011,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5031,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5045,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5059,7 +5056,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5073,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5087,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5098,10 +5095,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5115,7 +5112,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5129,7 +5126,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5143,7 +5140,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5157,7 +5154,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5171,7 +5168,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5185,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5199,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>270</v>
+        <v>477</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5213,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5227,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>356</v>
+        <v>479</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5241,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>269</v>
+        <v>480</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5280,7 +5277,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>483</v>
@@ -5322,7 +5319,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D248" t="s">
         <v>486</v>
@@ -5409,7 +5406,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>492</v>
+        <v>393</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5423,7 +5420,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5437,7 +5434,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="495">
   <si>
     <t>Filename</t>
   </si>
@@ -811,688 +811,694 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9649,0.0083,0.0073,0.0011</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9435,0.0002,0.0001,0.0631</t>
-  </si>
-  <si>
-    <t>0.3465,0.0001,0.0002,0.8495</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0001</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9660,0.0130,0.0015,0.0015</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9884,0.0002,0.0003,0.0077</t>
+  </si>
+  <si>
+    <t>0.0035,0.0000,0.0003,0.9983</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9973,0.0022,0.0001,0.0000</t>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9970,0.0002,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.0006,0.9921,0.0009</t>
-  </si>
-  <si>
-    <t>0.0936,0.0005,0.9610,0.0000</t>
-  </si>
-  <si>
-    <t>0.0356,0.0003,0.9798,0.0001</t>
-  </si>
-  <si>
-    <t>0.9667,0.0009,0.0245,0.0004</t>
+    <t>0.6961,0.0025,0.3227,0.0006</t>
+  </si>
+  <si>
+    <t>0.0084,0.0005,0.9922,0.0003</t>
+  </si>
+  <si>
+    <t>0.0325,0.0002,0.9834,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0003,0.9971,0.0003</t>
+  </si>
+  <si>
+    <t>0.9296,0.0004,0.0683,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0047,0.9940,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9978,0.0002,0.0004</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.9994,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.9967,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0909,0.0013,0.8837,0.0028</t>
-  </si>
-  <si>
-    <t>0.1436,0.0002,0.8658,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9981,0.0004</t>
-  </si>
-  <si>
-    <t>0.0092,0.0001,0.9960,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.0001,0.9955,0.0004</t>
-  </si>
-  <si>
-    <t>0.0378,0.0001,0.9783,0.0002</t>
-  </si>
-  <si>
-    <t>0.2639,0.7881,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.7832,0.0125,0.1457,0.0013</t>
-  </si>
-  <si>
-    <t>0.0009,0.0006,0.9991,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0003,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0979,0.9233,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9954,0.5845,0.0000</t>
-  </si>
-  <si>
-    <t>0.0046,0.9878,0.0040,0.0004</t>
-  </si>
-  <si>
-    <t>0.0038,0.0000,0.9940,0.0004</t>
-  </si>
-  <si>
-    <t>0.0015,0.0077,0.9951,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0009,0.9951,0.0015</t>
-  </si>
-  <si>
-    <t>0.0013,0.0454,0.9960,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9987,0.0013</t>
-  </si>
-  <si>
-    <t>0.0011,0.8686,0.0005,0.9602</t>
-  </si>
-  <si>
-    <t>0.0021,0.9963,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.9962,0.0027,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9996,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0008,0.9965,0.0008</t>
-  </si>
-  <si>
-    <t>0.0251,0.0001,0.9888,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0006,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9836,0.0192,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9972,0.9847,0.0000</t>
+    <t>0.8990,0.0009,0.0864,0.0011</t>
+  </si>
+  <si>
+    <t>0.8020,0.0007,0.2130,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.9985,0.0005</t>
+  </si>
+  <si>
+    <t>0.0013,0.0001,0.9975,0.0002</t>
+  </si>
+  <si>
+    <t>0.0076,0.0001,0.9947,0.0001</t>
+  </si>
+  <si>
+    <t>0.0110,0.0002,0.9860,0.0016</t>
+  </si>
+  <si>
+    <t>0.0396,0.0000,0.9774,0.0002</t>
+  </si>
+  <si>
+    <t>0.0779,0.9299,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.9630,0.0037,0.0208,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.0006,0.9992,0.0011</t>
+  </si>
+  <si>
+    <t>0.0017,0.9957,0.0021,0.0000</t>
+  </si>
+  <si>
+    <t>0.9888,0.0033,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.9970,0.0009,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.6800,0.3824,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9941,0.4180,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.9985,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0059,0.0005,0.9886,0.0005</t>
+  </si>
+  <si>
+    <t>0.0029,0.0097,0.9887,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9981,0.0016</t>
+  </si>
+  <si>
+    <t>0.0009,0.0007,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9983,0.0013</t>
+  </si>
+  <si>
+    <t>0.0074,0.5510,0.0006,0.9079</t>
+  </si>
+  <si>
+    <t>0.0008,0.9984,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0083,0.0000,0.9943,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0006,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0022,0.9998,0.0003</t>
+  </si>
+  <si>
+    <t>0.9808,0.0278,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9473,0.9892,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0144,0.9986,0.0015</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9987,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1731,0.0003,0.8891,0.0002</t>
+  </si>
+  <si>
+    <t>0.0208,0.0015,0.9784,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0030,0.9995,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.8512,0.9766,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.2647,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9776,0.8671,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0000,0.0024,0.9978</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0004,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0009,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.9939,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9962,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9911,0.8453,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.9948,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9964,0.0188,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0020,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0014,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0021,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9954,0.0031,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9797,0.0280,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0029,0.0004,0.9958,0.0002</t>
+  </si>
+  <si>
+    <t>0.8721,0.0023,0.0857,0.0030</t>
+  </si>
+  <si>
+    <t>0.6603,0.0001,0.3554,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9979,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.9975,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1989,0.8655,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.5928,0.0006,0.3841,0.0009</t>
+  </si>
+  <si>
+    <t>0.9955,0.0001,0.0031,0.0000</t>
+  </si>
+  <si>
+    <t>0.5969,0.0116,0.2777,0.0023</t>
+  </si>
+  <si>
+    <t>0.9478,0.0051,0.0127,0.0024</t>
+  </si>
+  <si>
+    <t>0.0007,0.6187,0.0007,0.9630</t>
+  </si>
+  <si>
+    <t>0.0004,0.9991,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9926,0.9872,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.6360,0.4557,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9785,0.0228,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0002,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0015,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.6769,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8434,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0012,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0032,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6977,0.0029,0.2448,0.0026</t>
+  </si>
+  <si>
+    <t>0.4114,0.0000,0.7773,0.0001</t>
+  </si>
+  <si>
+    <t>0.5242,0.0002,0.4729,0.0010</t>
+  </si>
+  <si>
+    <t>0.1013,0.0000,0.0000,0.9821</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.9551,0.8506,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0344,0.9647,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.4684,0.7022,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.8198,0.0000,0.0003,0.2738</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9987,0.0054</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0001,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0497,0.3723,0.3714,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9839,0.0029,0.0040,0.0005</t>
+  </si>
+  <si>
+    <t>0.5980,0.0247,0.1290,0.0019</t>
+  </si>
+  <si>
+    <t>0.8026,0.0016,0.2599,0.0001</t>
+  </si>
+  <si>
+    <t>0.9930,0.0012,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0009,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9820,0.0142,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.2020,0.8737,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.8780,0.1647,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0386,0.0010,0.9659,0.0006</t>
+  </si>
+  <si>
+    <t>0.9480,0.0732,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0002,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9960,0.0029,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9937,0.0011,0.0028,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9869,0.0053,0.0044,0.0003</t>
+  </si>
+  <si>
+    <t>0.0131,0.0573,0.9225,0.0019</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.0129,0.9910,0.0005</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0004,0.0040,0.9980,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9939,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7048,0.0002,0.4333,0.0001</t>
-  </si>
-  <si>
-    <t>0.7967,0.0026,0.1480,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.0012,0.9992,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.5235,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.8571,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9905,0.9828,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0016,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0011,0.9998</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9951,0.9792,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9982,0.9936,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9741,0.9145,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9900,0.9793,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9947,0.9934,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9915,0.3464,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9936,0.0036,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9953,0.0032,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0007,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0002,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.0153,0.0028,0.9782,0.0003</t>
-  </si>
-  <si>
-    <t>0.9832,0.0004,0.0064,0.0004</t>
-  </si>
-  <si>
-    <t>0.0098,0.0002,0.9905,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.9937,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9977,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.4063,0.6729,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.8249,0.0138,0.0721,0.0018</t>
-  </si>
-  <si>
-    <t>0.9748,0.0001,0.0243,0.0002</t>
-  </si>
-  <si>
-    <t>0.9441,0.0044,0.0093,0.0021</t>
-  </si>
-  <si>
-    <t>0.3736,0.0124,0.4935,0.0033</t>
-  </si>
-  <si>
-    <t>0.0045,0.7557,0.0067,0.8455</t>
-  </si>
-  <si>
-    <t>0.0006,0.9988,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9953,0.9755,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.2447,0.8057,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9101,0.1047,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0006,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9316,0.9959,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8777,0.9951,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0038,0.9962,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0004,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9314,0.0064,0.0073,0.0038</t>
-  </si>
-  <si>
-    <t>0.1082,0.0001,0.9332,0.0001</t>
-  </si>
-  <si>
-    <t>0.8041,0.0005,0.1817,0.0016</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9934,0.4918,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0136,0.9838,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.0166,0.9858,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9276,0.0000,0.0022,0.0441</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0015,0.9979,0.0014</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9941,0.0000,0.0025,0.0005</t>
-  </si>
-  <si>
-    <t>0.4786,0.2332,0.0562,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9703,0.0050,0.0080,0.0013</t>
-  </si>
-  <si>
-    <t>0.2020,0.0635,0.2994,0.0014</t>
-  </si>
-  <si>
-    <t>0.7441,0.0042,0.1642,0.0005</t>
-  </si>
-  <si>
-    <t>0.9938,0.0010,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0008,0.0005,0.0004</t>
+    <t>0.0000,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0191,0.0062,0.9684,0.0004</t>
+  </si>
+  <si>
+    <t>0.0323,0.0015,0.9667,0.0005</t>
+  </si>
+  <si>
+    <t>0.0152,0.0034,0.9755,0.0007</t>
+  </si>
+  <si>
+    <t>0.0145,0.0059,0.9702,0.0002</t>
+  </si>
+  <si>
+    <t>0.0771,0.1500,0.5904,0.0003</t>
+  </si>
+  <si>
+    <t>0.1069,0.0453,0.7489,0.0002</t>
+  </si>
+  <si>
+    <t>0.9255,0.0090,0.0229,0.0017</t>
+  </si>
+  <si>
+    <t>0.1547,0.0012,0.8939,0.0001</t>
+  </si>
+  <si>
+    <t>0.0490,0.9640,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8754,0.1743,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.1007,0.9314,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0668,0.9487,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9921,0.0004,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.8933,0.0002,0.1391,0.0003</t>
+  </si>
+  <si>
+    <t>0.9707,0.0013,0.0061,0.0022</t>
+  </si>
+  <si>
+    <t>0.7045,0.0212,0.2054,0.0065</t>
+  </si>
+  <si>
+    <t>0.3602,0.0001,0.7703,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.0002,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0023,0.9926,0.0013</t>
+  </si>
+  <si>
+    <t>0.0085,0.0090,0.9828,0.0005</t>
+  </si>
+  <si>
+    <t>0.0011,0.0004,0.9974,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0427,0.9770,0.0004</t>
+  </si>
+  <si>
+    <t>0.9958,0.0013,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9875,0.0064,0.0023,0.0018</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0014,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9995,0.0004</t>
+  </si>
+  <si>
+    <t>0.0393,0.0248,0.8503,0.0030</t>
+  </si>
+  <si>
+    <t>0.9820,0.0023,0.0067,0.0005</t>
+  </si>
+  <si>
+    <t>0.0017,0.0002,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.1087,0.9837,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.0002,0.9963,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0018,0.9965,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0098,0.9962,0.0004</t>
+  </si>
+  <si>
+    <t>0.9244,0.0090,0.0288,0.0010</t>
+  </si>
+  <si>
+    <t>0.9716,0.0001,0.0168,0.0007</t>
+  </si>
+  <si>
+    <t>0.9915,0.0005,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0013,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0014,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9995,0.0000,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9508,0.0328,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9484,0.0651,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.7876,0.2463,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.3012,0.0002,0.7378,0.0006</t>
-  </si>
-  <si>
-    <t>0.9870,0.0149,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0001,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9980,0.0011,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9823,0.0026,0.0075,0.0011</t>
-  </si>
-  <si>
-    <t>0.0017,0.0003,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.9950,0.0007,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.0154,0.9947,0.0021</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.2696,0.9883,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.1490,0.0015,0.8840,0.0004</t>
-  </si>
-  <si>
-    <t>0.0088,0.0007,0.9901,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.0036,0.9946,0.0001</t>
-  </si>
-  <si>
-    <t>0.5936,0.0081,0.3978,0.0003</t>
-  </si>
-  <si>
-    <t>0.2687,0.0533,0.3955,0.0008</t>
-  </si>
-  <si>
-    <t>0.9754,0.0006,0.0244,0.0001</t>
-  </si>
-  <si>
-    <t>0.9544,0.0014,0.0197,0.0016</t>
-  </si>
-  <si>
-    <t>0.0992,0.0225,0.8464,0.0009</t>
-  </si>
-  <si>
-    <t>0.0019,0.9970,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.9985,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.5818,0.4509,0.0040,0.0001</t>
-  </si>
-  <si>
-    <t>0.1688,0.8749,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0124,0.9871,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9942,0.0009,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9842,0.0001,0.0191,0.0001</t>
-  </si>
-  <si>
-    <t>0.9648,0.0014,0.0015,0.0054</t>
-  </si>
-  <si>
-    <t>0.9094,0.0132,0.0312,0.0024</t>
-  </si>
-  <si>
-    <t>0.8153,0.0005,0.1737,0.0009</t>
-  </si>
-  <si>
-    <t>0.0020,0.0006,0.9976,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0007,0.9980,0.0004</t>
-  </si>
-  <si>
-    <t>0.0159,0.0009,0.9763,0.0010</t>
-  </si>
-  <si>
-    <t>0.0062,0.0041,0.9871,0.0002</t>
-  </si>
-  <si>
-    <t>0.0016,0.0720,0.9232,0.0006</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9940,0.0031,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0014,0.9994,0.0005</t>
-  </si>
-  <si>
-    <t>0.0081,0.0144,0.9770,0.0008</t>
-  </si>
-  <si>
-    <t>0.9701,0.0002,0.0151,0.0014</t>
-  </si>
-  <si>
-    <t>0.0065,0.0003,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.6002,0.9917,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0662,0.0004,0.9593,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0002,0.9970,0.0011</t>
-  </si>
-  <si>
-    <t>0.0004,0.0047,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.3839,0.0023,0.6185,0.0009</t>
-  </si>
-  <si>
-    <t>0.9910,0.0002,0.0027,0.0002</t>
-  </si>
-  <si>
-    <t>0.9921,0.0002,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0019,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0064,0.0135,0.9746,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.1417,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0004,0.9948,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0171,0.0003,0.3839,0.2103</t>
-  </si>
-  <si>
-    <t>0.0495,0.0004,0.9518,0.0008</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9978,0.0011</t>
-  </si>
-  <si>
-    <t>0.7859,0.0000,0.0006,0.3053</t>
-  </si>
-  <si>
-    <t>0.0024,0.0002,0.0000,0.9994</t>
-  </si>
-  <si>
-    <t>0.0544,0.0000,0.0000,0.9960</t>
-  </si>
-  <si>
-    <t>0.9984,0.0001,0.0000,0.0001</t>
+    <t>0.9981,0.0019,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0030,0.9910,0.0007</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.3567,0.9977,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.0053,0.9893,0.0009</t>
+  </si>
+  <si>
+    <t>0.0011,0.0000,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9954,0.0026</t>
+  </si>
+  <si>
+    <t>0.1045,0.0015,0.8835,0.0011</t>
+  </si>
+  <si>
+    <t>0.0115,0.0014,0.9747,0.0041</t>
+  </si>
+  <si>
+    <t>0.9870,0.0000,0.0026,0.0032</t>
+  </si>
+  <si>
+    <t>0.0014,0.0008,0.0000,0.9994</t>
+  </si>
+  <si>
+    <t>0.0168,0.0000,0.0000,0.9978</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0000,0.0001</t>
   </si>
 </sst>
 </file>
@@ -1878,7 +1884,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1892,7 +1898,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1906,7 +1912,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1920,7 +1926,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1934,7 +1940,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1948,7 +1954,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1962,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1976,7 +1982,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1990,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2004,7 +2010,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2018,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2032,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2046,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2060,7 +2066,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2074,7 +2080,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2088,7 +2094,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2102,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2116,7 +2122,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2130,7 +2136,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2144,7 +2150,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2158,7 +2164,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2172,7 +2178,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2183,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2197,10 +2203,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2214,7 +2220,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2228,7 +2234,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2242,7 +2248,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2256,7 +2262,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2270,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2284,7 +2290,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2298,7 +2304,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2312,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2326,7 +2332,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2340,7 +2346,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2354,7 +2360,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2365,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2379,10 +2385,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2396,7 +2402,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2410,7 +2416,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2424,7 +2430,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2438,7 +2444,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2452,7 +2458,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2466,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2480,7 +2486,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2494,7 +2500,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2508,7 +2514,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2522,7 +2528,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2536,7 +2542,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2550,7 +2556,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2564,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2578,7 +2584,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2592,7 +2598,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2606,7 +2612,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2620,7 +2626,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2634,7 +2640,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2648,7 +2654,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2662,7 +2668,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2676,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2690,7 +2696,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2718,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>269</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2732,7 +2738,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2746,7 +2752,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2760,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2774,7 +2780,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2788,7 +2794,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2802,7 +2808,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2816,7 +2822,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2827,10 +2833,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2841,10 +2847,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2858,7 +2864,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2872,7 +2878,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2886,7 +2892,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2897,10 +2903,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2914,7 +2920,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2928,7 +2934,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2942,7 +2948,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2956,7 +2962,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2970,7 +2976,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2984,7 +2990,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2998,7 +3004,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3012,7 +3018,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3026,7 +3032,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3040,7 +3046,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3054,7 +3060,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3068,7 +3074,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3082,7 +3088,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3096,7 +3102,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3110,7 +3116,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>271</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3124,7 +3130,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3138,7 +3144,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>271</v>
+        <v>322</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3152,7 +3158,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3166,7 +3172,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3180,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3194,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3208,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3222,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3236,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3250,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3264,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>316</v>
+        <v>273</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3278,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3292,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3306,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3320,7 +3326,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3334,7 +3340,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3348,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3359,10 +3365,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D108" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3376,7 +3382,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3390,7 +3396,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3404,7 +3410,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3418,7 +3424,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3432,7 +3438,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3446,7 +3452,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3460,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3474,7 +3480,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3488,7 +3494,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3502,7 +3508,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3516,7 +3522,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3530,7 +3536,7 @@
         <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3544,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3558,7 +3564,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3572,7 +3578,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3586,7 +3592,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3600,7 +3606,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3611,10 +3617,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3628,7 +3634,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3642,7 +3648,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3656,7 +3662,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3670,7 +3676,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3684,7 +3690,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3698,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>380</v>
+        <v>318</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3712,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3726,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3740,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3754,7 +3760,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3768,7 +3774,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3782,7 +3788,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3796,7 +3802,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3810,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3824,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3838,7 +3844,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3852,7 +3858,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3866,7 +3872,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3880,7 +3886,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>393</v>
+        <v>339</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3894,7 +3900,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>337</v>
+        <v>395</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3908,7 +3914,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3919,10 +3925,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3936,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3950,7 +3956,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3964,7 +3970,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>271</v>
+        <v>400</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3978,7 +3984,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3992,7 +3998,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4006,7 +4012,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4020,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>400</v>
+        <v>273</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4034,7 +4040,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4048,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4062,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4073,10 +4079,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D159" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4090,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4104,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4118,7 +4124,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4132,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4146,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4160,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4174,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4188,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4202,7 +4208,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4216,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4230,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4244,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>415</v>
+        <v>318</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4258,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4272,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4283,10 +4289,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4300,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4314,7 +4320,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4328,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4342,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4356,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4370,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4384,7 +4390,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4398,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4412,7 +4418,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4426,7 +4432,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4440,7 +4446,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4454,7 +4460,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4468,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4482,7 +4488,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4496,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4510,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4524,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4538,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4549,10 +4555,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4563,10 +4569,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4577,10 +4583,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4594,7 +4600,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4608,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4622,7 +4628,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4636,7 +4642,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4650,7 +4656,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4664,7 +4670,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4678,7 +4684,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4692,7 +4698,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4706,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4720,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4734,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4745,10 +4751,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4762,7 +4768,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4776,7 +4782,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4790,7 +4796,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4804,7 +4810,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4818,7 +4824,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4832,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>378</v>
+        <v>322</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4846,7 +4852,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4860,7 +4866,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4874,7 +4880,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4888,7 +4894,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4902,7 +4908,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4916,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4930,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>380</v>
+        <v>274</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4944,7 +4950,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4958,7 +4964,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4972,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4986,7 +4992,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5000,7 +5006,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5011,10 +5017,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5028,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5042,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5056,7 +5062,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5070,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5084,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5095,10 +5101,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5112,7 +5118,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5126,7 +5132,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5140,7 +5146,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>474</v>
+        <v>322</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5154,7 +5160,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5168,7 +5174,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5182,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5196,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5210,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5224,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5238,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>480</v>
+        <v>272</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5252,7 +5258,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5266,7 +5272,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5280,7 +5286,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5294,7 +5300,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5308,7 +5314,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5319,10 +5325,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5336,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5350,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5364,7 +5370,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5378,7 +5384,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5392,7 +5398,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5406,7 +5412,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>393</v>
+        <v>339</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5420,7 +5426,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>393</v>
+        <v>339</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5434,7 +5440,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
